--- a/Výsledky/sk_bpe_blm.xlsx
+++ b/Výsledky/sk_bpe_blm.xlsx
@@ -7689,7 +7689,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>W</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">

--- a/Výsledky/sk_bpe_blm.xlsx
+++ b/Výsledky/sk_bpe_blm.xlsx
@@ -793,16 +793,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>O</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
       <c r="E15" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3477,7 +3477,7 @@
         </is>
       </c>
       <c r="E122" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>O</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E125" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -6843,7 +6843,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="E257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>V</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -7502,7 +7502,7 @@
         </is>
       </c>
       <c r="E283" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="284">
@@ -17789,7 +17789,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
@@ -17798,7 +17798,7 @@
         </is>
       </c>
       <c r="E695" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="696">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -18764,7 +18764,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -18773,7 +18773,7 @@
         </is>
       </c>
       <c r="E734" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="735">
@@ -22914,7 +22914,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>S</t>
         </is>
       </c>
       <c r="D900" t="inlineStr">
@@ -22923,7 +22923,7 @@
         </is>
       </c>
       <c r="E900" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="901">
@@ -29114,7 +29114,7 @@
       </c>
       <c r="C1148" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D1148" t="inlineStr">
@@ -29123,7 +29123,7 @@
         </is>
       </c>
       <c r="E1148" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1149">

--- a/Výsledky/sk_bpe_blm.xlsx
+++ b/Výsledky/sk_bpe_blm.xlsx
@@ -3618,7 +3618,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -18014,7 +18014,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="E704" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="705">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">

--- a/Výsledky/sk_bpe_blm.xlsx
+++ b/Výsledky/sk_bpe_blm.xlsx
@@ -7616,8 +7616,10 @@
           <t>29</t>
         </is>
       </c>
-      <c r="C288" t="n">
-        <v>0</v>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -7664,8 +7666,10 @@
           <t>8</t>
         </is>
       </c>
-      <c r="C290" t="n">
-        <v>0</v>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
